--- a/templates/oc_modelo.xlsx
+++ b/templates/oc_modelo.xlsx
@@ -691,7 +691,7 @@
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="299">
+  <cellXfs count="301">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1563,6 +1563,8 @@
     <xf numFmtId="4" fontId="33" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="20">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2416,7 +2418,7 @@
       </c>
       <c r="G31" s="260" t="inlineStr">
         <is>
-          <t>VALOR UNITÁIO</t>
+          <t>VALOR UNITÁRIO</t>
         </is>
       </c>
       <c r="H31" s="267" t="inlineStr">
@@ -2435,7 +2437,7 @@
       <c r="C32" s="269" t="n"/>
       <c r="D32" s="269" t="n"/>
       <c r="E32" s="172" t="n"/>
-      <c r="F32" s="172" t="inlineStr">
+      <c r="F32" s="171" t="inlineStr">
         <is>
           <t>PC</t>
         </is>
@@ -2454,7 +2456,7 @@
       <c r="C33" s="269" t="n"/>
       <c r="D33" s="269" t="n"/>
       <c r="E33" s="172" t="n"/>
-      <c r="F33" s="172" t="inlineStr">
+      <c r="F33" s="171" t="inlineStr">
         <is>
           <t>PC</t>
         </is>
@@ -2466,42 +2468,57 @@
       </c>
     </row>
     <row r="34" ht="84.75" customHeight="1" s="175">
-      <c r="B34" s="268" t="n"/>
+      <c r="B34" s="268">
+        <f>B33+1</f>
+        <v/>
+      </c>
       <c r="C34" s="269" t="n"/>
       <c r="D34" s="269" t="n"/>
-      <c r="F34" s="172" t="inlineStr">
+      <c r="E34" s="299" t="n"/>
+      <c r="F34" s="171" t="inlineStr">
         <is>
           <t>PC</t>
         </is>
       </c>
+      <c r="G34" s="300" t="n"/>
       <c r="H34" s="270">
         <f>G34*E34</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="84.75" customHeight="1" s="175">
-      <c r="B35" s="268" t="n"/>
+      <c r="B35" s="268">
+        <f>B34+1</f>
+        <v/>
+      </c>
       <c r="C35" s="269" t="n"/>
       <c r="D35" s="269" t="n"/>
-      <c r="F35" s="172" t="inlineStr">
+      <c r="E35" s="299" t="n"/>
+      <c r="F35" s="171" t="inlineStr">
         <is>
           <t>PC</t>
         </is>
       </c>
+      <c r="G35" s="300" t="n"/>
       <c r="H35" s="270">
         <f>G35*E35</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="46.5" customHeight="1" s="175">
-      <c r="B36" s="268" t="n"/>
+      <c r="B36" s="268">
+        <f>B35+1</f>
+        <v/>
+      </c>
       <c r="C36" s="269" t="n"/>
       <c r="D36" s="269" t="n"/>
+      <c r="E36" s="299" t="n"/>
       <c r="F36" s="171" t="inlineStr">
         <is>
           <t>PC</t>
         </is>
       </c>
+      <c r="G36" s="300" t="n"/>
       <c r="H36" s="270">
         <f>G36*E36</f>
         <v/>

--- a/templates/oc_modelo.xlsx
+++ b/templates/oc_modelo.xlsx
@@ -2642,7 +2642,7 @@
         </is>
       </c>
       <c r="H50" s="280">
-        <f>H38+H40+H42+H44+H46+H48</f>
+        <f>H38-H40+H42+H44+H46+H48</f>
         <v/>
       </c>
       <c r="K50" s="281" t="n"/>
